--- a/dokumenti/aktivni.xlsx
+++ b/dokumenti/aktivni.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://finkiukim-my.sharepoint.com/personal/mila_dodevska_finki_ukim_mk/Documents/BIP2026/dokumenti/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="216" documentId="11_F25DC773A252ABDACC104839111B439C5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7DEA0EE-4A00-4ABB-A027-A9B79550417B}"/>
+  <xr:revisionPtr revIDLastSave="395" documentId="11_F25DC773A252ABDACC104839111B439C5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F56F6266-A5C8-4246-8A3E-B793FAA50E24}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="210">
   <si>
     <t>No.</t>
   </si>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">1 June / 1 November </t>
   </si>
   <si>
-    <t>ured@inf.uniri.hr (Faculty of Informatics)</t>
+    <t xml:space="preserve">ured@inf.uniri.hr </t>
   </si>
   <si>
     <t>FRANCE</t>
@@ -539,7 +539,7 @@
     <t>Information and Communication Technologies (ICTs)</t>
   </si>
   <si>
-    <t>rektorluk@mehmetakif.edu.tr , iro@mehmetakif.edu.tr (Erasmus office)</t>
+    <t xml:space="preserve">rektorluk@mehmetakif.edu.tr , iro@mehmetakif.edu.tr </t>
   </si>
   <si>
     <t>Trabzon University</t>
@@ -580,13 +580,104 @@
   </si>
   <si>
     <t>erasmus@khas.edu.tr</t>
+  </si>
+  <si>
+    <t>SERBIA</t>
+  </si>
+  <si>
+    <t>UNIVERZITET U NISU</t>
+  </si>
+  <si>
+    <t>https://www.ni.ac.rs/en/</t>
+  </si>
+  <si>
+    <t>RS NIS01</t>
+  </si>
+  <si>
+    <t>ISCED</t>
+  </si>
+  <si>
+    <t>1st cycle 4х5 months (20)</t>
+  </si>
+  <si>
+    <t>15 May / 15 November</t>
+  </si>
+  <si>
+    <t>mobility@ni.ac.rs</t>
+  </si>
+  <si>
+    <t>GREECE</t>
+  </si>
+  <si>
+    <t>DIETHNES PANEPISTIMIO ELLADOS, International Hellenic
+University</t>
+  </si>
+  <si>
+    <t>https://www.ihu.gr/en/academic-units/intprogsen</t>
+  </si>
+  <si>
+    <t>G THES
+SAL14</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Information and communication Technologies (ICTS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 June / 30 November </t>
+  </si>
+  <si>
+    <t>erasmus.in@the.ihu.gr</t>
+  </si>
+  <si>
+    <t>UNIVERZA V MARIBORU, Faculty of Electrical Engineering and
+Computer Science</t>
+  </si>
+  <si>
+    <t>https://www.um.si/en/international/erasm us</t>
+  </si>
+  <si>
+    <t>SI MARI BOR01</t>
+  </si>
+  <si>
+    <t>incoming.erasmus@um.si</t>
+  </si>
+  <si>
+    <t>UNIVERZA V NOVI GORICI, School of Engineering and Management</t>
+  </si>
+  <si>
+    <t>University of Nova Gorica</t>
+  </si>
+  <si>
+    <t>SI NOVA--GO01</t>
+  </si>
+  <si>
+    <t>2022 - 2029</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Engineering and engineering trades</t>
+  </si>
+  <si>
+    <t>international.office@ung.si</t>
+  </si>
+  <si>
+    <t>INSTITUTO POLITECNICO DA GUARDA</t>
+  </si>
+  <si>
+    <t>Politécnico da Guarda — O potencial do nosso interior.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P GUAR
+DA01</t>
+  </si>
+  <si>
+    <t>incoming@ipg.pt</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -621,6 +712,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -636,7 +749,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -659,12 +772,82 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -675,17 +858,107 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -694,7 +967,15 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <name val="Arial"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+      </border>
     </dxf>
     <dxf>
       <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -745,10 +1026,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1034,23 +1311,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB12D38F-D87F-4F8B-8166-8B6AF04B00C1}">
-  <dimension ref="A1:K25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AI30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="18.26953125" customWidth="1"/>
-    <col min="5" max="5" width="18.453125" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" customWidth="1"/>
-    <col min="7" max="7" width="20.7265625" customWidth="1"/>
-    <col min="8" max="8" width="20.1796875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" customWidth="1"/>
+    <col min="8" max="8" width="20.140625" customWidth="1"/>
     <col min="9" max="9" width="31" customWidth="1"/>
-    <col min="10" max="10" width="13.54296875" style="6" customWidth="1"/>
-    <col min="11" max="11" width="22.453125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="22.42578125" style="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="56" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="57.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1078,14 +1355,14 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="39" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="42" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="43.5">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1113,14 +1390,14 @@
       <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="39" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="56" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="43.5">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1148,14 +1425,14 @@
       <c r="I3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="39" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="42" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="43.5">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1183,14 +1460,14 @@
       <c r="I4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="39" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="28.5">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1218,14 +1495,14 @@
       <c r="I5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="40" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="42" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="43.5">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1253,14 +1530,14 @@
       <c r="I6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="41" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="42" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="43.5">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1288,14 +1565,14 @@
       <c r="I7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="39" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="42" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="43.5">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1323,14 +1600,14 @@
       <c r="I8" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="39" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="42" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="43.5">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1358,14 +1635,14 @@
       <c r="I9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="39" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="42" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="43.5">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1393,14 +1670,14 @@
       <c r="I10" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="39" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="42" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="43.5">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1428,14 +1705,14 @@
       <c r="I11" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="39" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="42" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="43.5">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1463,14 +1740,14 @@
       <c r="I12" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="K12" s="39" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="42" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" ht="43.5">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1498,14 +1775,14 @@
       <c r="I13" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="39" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="42" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" ht="43.5">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1533,14 +1810,14 @@
       <c r="I14" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="K14" s="6" t="s">
+      <c r="K14" s="39" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="42" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="43.5">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1568,14 +1845,14 @@
       <c r="I15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="J15" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="K15" s="6" t="s">
+      <c r="K15" s="39" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="42" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" ht="43.5">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1603,14 +1880,14 @@
       <c r="I16" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="K16" s="39" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="42" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:35" ht="43.5">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1638,14 +1915,14 @@
       <c r="I17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="J17" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" s="36" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="42" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:35" ht="43.5">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1673,14 +1950,14 @@
       <c r="I18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="J18" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K18" s="38" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="42" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:35" ht="57.75">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1708,14 +1985,14 @@
       <c r="I19" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="J19" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K19" s="36" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="28" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:35" ht="28.5">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1743,14 +2020,14 @@
       <c r="I20" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="J20" s="5" t="s">
+      <c r="J20" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" s="39" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="42" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:35" ht="43.5">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1778,14 +2055,14 @@
       <c r="I21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21" s="42" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:35" ht="43.5">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1813,14 +2090,14 @@
       <c r="I22" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="J22" s="32" t="s">
         <v>161</v>
       </c>
-      <c r="K22" s="6" t="s">
+      <c r="K22" s="39" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:35" ht="45.75">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1848,14 +2125,14 @@
       <c r="I23" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J23" s="5" t="s">
+      <c r="J23" s="32" t="s">
         <v>161</v>
       </c>
-      <c r="K23" s="6" t="s">
+      <c r="K23" s="40" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="42" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:35" ht="43.5">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1883,47 +2160,328 @@
       <c r="I24" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="J24" s="5" t="s">
+      <c r="J24" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="K24" s="7" t="s">
+      <c r="K24" s="41" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="42" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:35" ht="45.75">
       <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="I25" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J25" s="5" t="s">
+      <c r="J25" s="33" t="s">
         <v>179</v>
       </c>
-      <c r="K25" s="6" t="s">
+      <c r="K25" s="39" t="s">
         <v>180</v>
       </c>
+    </row>
+    <row r="26" spans="1:35" s="15" customFormat="1" ht="30.75">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="J26" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="K26" s="41" t="s">
+        <v>188</v>
+      </c>
+      <c r="L26"/>
+      <c r="M26"/>
+      <c r="N26"/>
+      <c r="O26"/>
+      <c r="P26"/>
+      <c r="Q26"/>
+      <c r="R26"/>
+      <c r="S26"/>
+      <c r="T26"/>
+      <c r="U26"/>
+      <c r="V26"/>
+      <c r="W26"/>
+      <c r="X26"/>
+      <c r="Y26"/>
+      <c r="Z26"/>
+      <c r="AA26"/>
+      <c r="AB26"/>
+      <c r="AC26"/>
+      <c r="AD26"/>
+      <c r="AE26"/>
+      <c r="AF26"/>
+      <c r="AG26"/>
+      <c r="AH26"/>
+      <c r="AI26" s="27"/>
+    </row>
+    <row r="27" spans="1:35" s="12" customFormat="1" ht="72">
+      <c r="A27" s="43">
+        <v>26</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J27" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="K27" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="30"/>
+      <c r="P27" s="30"/>
+      <c r="Q27" s="30"/>
+      <c r="R27" s="30"/>
+      <c r="S27" s="30"/>
+      <c r="T27" s="30"/>
+      <c r="U27" s="30"/>
+      <c r="V27" s="30"/>
+      <c r="W27" s="30"/>
+      <c r="X27" s="30"/>
+      <c r="Y27" s="30"/>
+      <c r="Z27" s="30"/>
+      <c r="AA27" s="30"/>
+      <c r="AB27" s="30"/>
+      <c r="AC27" s="30"/>
+      <c r="AD27" s="30"/>
+      <c r="AE27" s="30"/>
+      <c r="AF27" s="30"/>
+      <c r="AG27" s="30"/>
+      <c r="AH27" s="30"/>
+      <c r="AI27" s="28"/>
+    </row>
+    <row r="28" spans="1:35" s="12" customFormat="1" ht="72">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J28" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="K28" s="36" t="s">
+        <v>199</v>
+      </c>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
+      <c r="P28" s="30"/>
+      <c r="Q28" s="30"/>
+      <c r="R28" s="30"/>
+      <c r="S28" s="30"/>
+      <c r="T28" s="30"/>
+      <c r="U28" s="30"/>
+      <c r="V28" s="30"/>
+      <c r="W28" s="30"/>
+      <c r="X28" s="30"/>
+      <c r="Y28" s="30"/>
+      <c r="Z28" s="30"/>
+      <c r="AA28" s="30"/>
+      <c r="AB28" s="30"/>
+      <c r="AC28" s="30"/>
+      <c r="AD28" s="30"/>
+      <c r="AE28" s="30"/>
+      <c r="AF28" s="30"/>
+      <c r="AG28" s="30"/>
+      <c r="AH28" s="30"/>
+      <c r="AI28" s="28"/>
+    </row>
+    <row r="29" spans="1:35" s="12" customFormat="1" ht="57.75">
+      <c r="A29" s="19">
+        <v>28</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="H29" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J29" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="K29" s="36" t="s">
+        <v>205</v>
+      </c>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="30"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
+      <c r="AA29" s="30"/>
+      <c r="AB29" s="30"/>
+      <c r="AC29" s="30"/>
+      <c r="AD29" s="30"/>
+      <c r="AE29" s="30"/>
+      <c r="AF29" s="30"/>
+      <c r="AG29" s="30"/>
+      <c r="AH29" s="30"/>
+      <c r="AI29" s="28"/>
+    </row>
+    <row r="30" spans="1:35" s="9" customFormat="1" ht="60.75">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J30" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="K30" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="30"/>
+      <c r="P30" s="30"/>
+      <c r="Q30" s="30"/>
+      <c r="R30" s="30"/>
+      <c r="S30" s="30"/>
+      <c r="T30" s="30"/>
+      <c r="U30" s="30"/>
+      <c r="V30" s="30"/>
+      <c r="W30" s="30"/>
+      <c r="X30" s="30"/>
+      <c r="Y30" s="30"/>
+      <c r="Z30" s="30"/>
+      <c r="AA30" s="30"/>
+      <c r="AB30" s="30"/>
+      <c r="AC30" s="30"/>
+      <c r="AD30" s="30"/>
+      <c r="AE30" s="30"/>
+      <c r="AF30" s="30"/>
+      <c r="AG30" s="30"/>
+      <c r="AH30" s="30"/>
+      <c r="AI30" s="29"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -1954,10 +2512,20 @@
     <hyperlink ref="D25" r:id="rId24" xr:uid="{86EB118F-5689-45E6-8773-F0150709BB70}"/>
     <hyperlink ref="K6" r:id="rId25" xr:uid="{72BED157-B21C-414F-9997-551ACF4FA118}"/>
     <hyperlink ref="K24" r:id="rId26" xr:uid="{3434208E-6E33-4EAF-8046-2AD5F1C8ED6C}"/>
+    <hyperlink ref="D26" r:id="rId27" xr:uid="{FB64AB35-63B3-42E8-B12B-B665BC69C2E7}"/>
+    <hyperlink ref="K26" r:id="rId28" xr:uid="{702125EA-B866-4A38-A1E8-94D5CBF589BB}"/>
+    <hyperlink ref="D27" r:id="rId29" xr:uid="{F5C60BC8-BC48-4992-A0FA-0E5ADF758253}"/>
+    <hyperlink ref="K27" r:id="rId30" xr:uid="{FF444ED8-F9A0-491C-8038-B106269C800F}"/>
+    <hyperlink ref="D29" r:id="rId31" xr:uid="{246F8DF6-7F59-4058-B2D9-770C6D34AFA4}"/>
+    <hyperlink ref="K30" r:id="rId32" xr:uid="{9D384B90-7A83-4489-981E-A04C3DDEE260}"/>
+    <hyperlink ref="D30" r:id="rId33" xr:uid="{7FFC90F2-011A-49F7-AD5F-D18ADBD6E6E0}"/>
+    <hyperlink ref="K18" r:id="rId34" xr:uid="{40645B1F-629C-42C6-9D02-5B3AE6DD1ADE}"/>
+    <hyperlink ref="K5" r:id="rId35" xr:uid="{61AA9D81-F3F8-49A5-922D-BE200A95238C}"/>
+    <hyperlink ref="K23" r:id="rId36" xr:uid="{2C8C264F-A5FB-4BEF-92C9-6662EE070758}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId27"/>
+    <tablePart r:id="rId37"/>
   </tableParts>
 </worksheet>
 </file>